--- a/outputs/radio-budget.xlsx
+++ b/outputs/radio-budget.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бюджет запуска" sheetId="1" r:id="R3727e438201b4b89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бюджет запуска" sheetId="1" r:id="Re3a8b5383d1b43f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -106,7 +106,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -131,10 +131,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -151,19 +151,16 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -374,12 +371,12 @@
   </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -415,182 +412,142 @@
         <x:v>Разовые расходы</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>Количество</x:v>
+        <x:v>Цена, ₽</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
-        <x:v>Цена, ₽</x:v>
+        <x:v>Статус</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>Сумма, ₽</x:v>
-      </x:c>
-      <x:c r="E4" s="13" t="str">
-        <x:v>Статус</x:v>
-      </x:c>
-      <x:c r="F4" s="13" t="str">
         <x:v>Комментарий</x:v>
       </x:c>
+      <x:c r="E4" s="24"/>
+      <x:c r="F4" s="24"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
         <x:v>RadioBOSS Standard</x:v>
       </x:c>
       <x:c r="B5" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="27" t="n">
         <x:v>6599</x:v>
       </x:c>
-      <x:c r="D5" s="28" t="n">
-        <x:f>B5*C5</x:f>
-        <x:v>6599</x:v>
-      </x:c>
-      <x:c r="E5" s="25" t="str">
+      <x:c r="C5" s="25" t="str">
         <x:v>Нужно купить</x:v>
       </x:c>
-      <x:c r="F5" s="25" t="str">
+      <x:c r="D5" s="25" t="str">
         <x:v>Для физического лица; бессрочная лицензия</x:v>
       </x:c>
+      <x:c r="E5" s="24"/>
+      <x:c r="F5" s="24"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="25" t="str">
         <x:v>RadioBOSS Advanced</x:v>
       </x:c>
       <x:c r="B6" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="27" t="n">
         <x:v>8299</x:v>
       </x:c>
-      <x:c r="D6" s="28" t="n">
-        <x:f>B6*C6</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="25" t="str">
+      <x:c r="C6" s="25" t="str">
         <x:v>Вариант</x:v>
       </x:c>
-      <x:c r="F6" s="25" t="str">
+      <x:c r="D6" s="25" t="str">
         <x:v>Можно выбрать вместо Standard</x:v>
       </x:c>
+      <x:c r="E6" s="24"/>
+      <x:c r="F6" s="24"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="25" t="str">
         <x:v>Сервер: переезд на VPS 4 CPU / 4 ГБ RAM</x:v>
       </x:c>
       <x:c r="B7" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="27" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="28" t="n">
-        <x:f>B7*C7</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="25" t="str">
+      <x:c r="C7" s="25" t="str">
         <x:v>Оценить</x:v>
       </x:c>
-      <x:c r="F7" s="25" t="str">
+      <x:c r="D7" s="25" t="str">
         <x:v>Стоимость учитывается в ежемесячных расходах</x:v>
       </x:c>
+      <x:c r="E7" s="24"/>
+      <x:c r="F7" s="24"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="25" t="str">
         <x:v>Микрофон</x:v>
       </x:c>
       <x:c r="B8" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="27" t="n">
         <x:v>15000</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="n">
-        <x:f>B8*C8</x:f>
-        <x:v>15000</x:v>
-      </x:c>
-      <x:c r="E8" s="25" t="str">
+      <x:c r="C8" s="25" t="str">
         <x:v>Если нет</x:v>
       </x:c>
-      <x:c r="F8" s="25" t="str">
+      <x:c r="D8" s="25" t="str">
         <x:v>Средний ориентир</x:v>
       </x:c>
+      <x:c r="E8" s="24"/>
+      <x:c r="F8" s="24"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="25" t="str">
         <x:v>Звуковая карта / аудиоинтерфейс</x:v>
       </x:c>
       <x:c r="B9" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="27" t="n">
         <x:v>12000</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="n">
-        <x:f>B9*C9</x:f>
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="E9" s="25" t="str">
+      <x:c r="C9" s="25" t="str">
         <x:v>Если нет</x:v>
       </x:c>
-      <x:c r="F9" s="25" t="str">
+      <x:c r="D9" s="25" t="str">
         <x:v>Средний ориентир</x:v>
       </x:c>
+      <x:c r="E9" s="24"/>
+      <x:c r="F9" s="24"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="25" t="str">
         <x:v>Кабели, стойка, мелкие аксессуары</x:v>
       </x:c>
       <x:c r="B10" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="27" t="n">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="n">
-        <x:f>B10*C10</x:f>
-        <x:v>5000</x:v>
-      </x:c>
-      <x:c r="E10" s="25" t="str">
+      <x:c r="C10" s="25" t="str">
         <x:v>Если нет</x:v>
       </x:c>
-      <x:c r="F10" s="25" t="str">
+      <x:c r="D10" s="25" t="str">
         <x:v>Резерв на подключение</x:v>
       </x:c>
+      <x:c r="E10" s="24"/>
+      <x:c r="F10" s="24"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="25" t="str">
         <x:v>Первичная настройка и тестирование</x:v>
       </x:c>
       <x:c r="B11" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="27" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="n">
-        <x:f>B11*C11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="25" t="str">
+      <x:c r="C11" s="25" t="str">
         <x:v>Своими силами</x:v>
       </x:c>
-      <x:c r="F11" s="25" t="str">
+      <x:c r="D11" s="25" t="str">
         <x:v>При самостоятельной настройке</x:v>
       </x:c>
+      <x:c r="E11" s="24"/>
+      <x:c r="F11" s="24"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="25" t="str">
+      <x:c r="A12" s="27" t="str">
         <x:v>Итого разовые расходы</x:v>
       </x:c>
-      <x:c r="B12" s="25"/>
-      <x:c r="C12" s="28"/>
-      <x:c r="D12" s="29" t="n">
-        <x:f>SUM(D5:D11)</x:f>
+      <x:c r="B12" s="28" t="n">
         <x:v>38599</x:v>
       </x:c>
-      <x:c r="E12" s="30"/>
-      <x:c r="F12" s="30" t="str">
+      <x:c r="C12" s="27" t="str"/>
+      <x:c r="D12" s="27" t="str">
         <x:v>Без учёта необязательного Advanced</x:v>
       </x:c>
+      <x:c r="E12" s="24"/>
+      <x:c r="F12" s="24"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="24"/>
@@ -613,56 +570,42 @@
         <x:v>Ежемесячные расходы</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>Количество</x:v>
+        <x:v>Цена, ₽/мес</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
-        <x:v>Цена, ₽/мес</x:v>
-      </x:c>
-      <x:c r="D15" s="13" t="str">
-        <x:v>Сумма, ₽/мес</x:v>
-      </x:c>
-      <x:c r="E15" s="13" t="str">
         <x:v>Комментарий</x:v>
       </x:c>
-      <x:c r="F15" s="13"/>
+      <x:c r="D15" s="24"/>
+      <x:c r="E15" s="24"/>
+      <x:c r="F15" s="24"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="25" t="str">
         <x:v>VPS для AzuraCast</x:v>
       </x:c>
       <x:c r="B16" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="D16" s="28" t="n">
-        <x:f>B16*C16</x:f>
-        <x:v>1200</x:v>
-      </x:c>
-      <x:c r="E16" s="25" t="str">
+      <x:c r="C16" s="25" t="str">
         <x:v>Ориентир для 4 CPU / 4 ГБ RAM; текущий сервер слабоват для надёжной работы</x:v>
       </x:c>
-      <x:c r="F16" s="25"/>
+      <x:c r="D16" s="24"/>
+      <x:c r="E16" s="24"/>
+      <x:c r="F16" s="24"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="25" t="str">
         <x:v>Резервные копии</x:v>
       </x:c>
       <x:c r="B17" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D17" s="28" t="n">
-        <x:f>B17*C17</x:f>
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="E17" s="25" t="str">
+      <x:c r="C17" s="25" t="str">
         <x:v>Ориентир; зависит от выбранного хранилища</x:v>
       </x:c>
-      <x:c r="F17" s="25"/>
+      <x:c r="D17" s="24"/>
+      <x:c r="E17" s="24"/>
+      <x:c r="F17" s="24"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="25" t="str">
@@ -671,51 +614,40 @@
       <x:c r="B18" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="28" t="n">
-        <x:f>B18*C18</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E18" s="25" t="str">
+      <x:c r="C18" s="25" t="str">
         <x:v>Не обязательно: купленная лицензия продолжает работать</x:v>
       </x:c>
-      <x:c r="F18" s="25"/>
+      <x:c r="D18" s="24"/>
+      <x:c r="E18" s="24"/>
+      <x:c r="F18" s="24"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="25" t="str">
         <x:v>Музыкальные права</x:v>
       </x:c>
       <x:c r="B19" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D19" s="28" t="n">
-        <x:f>B19*C19</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E19" s="25" t="str">
+      <x:c r="C19" s="25" t="str">
         <x:v>Нужно определить отдельно по каталогу музыки</x:v>
       </x:c>
-      <x:c r="F19" s="25"/>
+      <x:c r="D19" s="24"/>
+      <x:c r="E19" s="24"/>
+      <x:c r="F19" s="24"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="25" t="str">
+      <x:c r="A20" s="27" t="str">
         <x:v>Итого ежемесячно</x:v>
       </x:c>
-      <x:c r="B20" s="25"/>
-      <x:c r="C20" s="28"/>
-      <x:c r="D20" s="29" t="n">
-        <x:f>SUM(D16:D19)</x:f>
+      <x:c r="B20" s="28" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="E20" s="30" t="str">
+      <x:c r="C20" s="27" t="str">
         <x:v>Расчёт в рублях</x:v>
       </x:c>
-      <x:c r="F20" s="30"/>
+      <x:c r="D20" s="24"/>
+      <x:c r="E20" s="24"/>
+      <x:c r="F20" s="24"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="24"/>
@@ -738,101 +670,77 @@
         <x:v>Ключевые итоги</x:v>
       </x:c>
       <x:c r="B23" s="13" t="str">
-        <x:v>Значение</x:v>
+        <x:v>Значение, ₽</x:v>
       </x:c>
       <x:c r="C23" s="13" t="str">
-        <x:v>Единица</x:v>
-      </x:c>
-      <x:c r="D23" s="13" t="str">
-        <x:v>Расчёт</x:v>
-      </x:c>
-      <x:c r="E23" s="13" t="str">
         <x:v>Примечание</x:v>
       </x:c>
+      <x:c r="D23" s="24"/>
+      <x:c r="E23" s="24"/>
       <x:c r="F23" s="24"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="25" t="str">
+      <x:c r="A24" s="27" t="str">
         <x:v>Старт без новой техники</x:v>
       </x:c>
-      <x:c r="B24" s="27" t="n">
-        <x:f>D5</x:f>
+      <x:c r="B24" s="29" t="n">
         <x:v>6599</x:v>
       </x:c>
       <x:c r="C24" s="25" t="str">
-        <x:v>₽</x:v>
-      </x:c>
-      <x:c r="D24" s="25" t="str">
-        <x:v>RadioBOSS + без техники</x:v>
-      </x:c>
-      <x:c r="E24" s="25" t="str">
         <x:v>Если микрофон и аудиокарта уже есть</x:v>
       </x:c>
+      <x:c r="D24" s="24"/>
+      <x:c r="E24" s="24"/>
       <x:c r="F24" s="24"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="30" t="str">
+      <x:c r="A25" s="27" t="str">
         <x:v>Старт с техникой</x:v>
       </x:c>
-      <x:c r="B25" s="29" t="n">
-        <x:f>D12</x:f>
+      <x:c r="B25" s="28" t="n">
         <x:v>38599</x:v>
       </x:c>
       <x:c r="C25" s="25" t="str">
-        <x:v>₽</x:v>
-      </x:c>
-      <x:c r="D25" s="25" t="str">
-        <x:v>RadioBOSS + микрофон + интерфейс + кабели</x:v>
-      </x:c>
-      <x:c r="E25" s="25" t="str">
         <x:v>Текущая оценка</x:v>
       </x:c>
+      <x:c r="D25" s="24"/>
+      <x:c r="E25" s="24"/>
       <x:c r="F25" s="24"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="27" t="str">
         <x:v>Первый год эксплуатации</x:v>
       </x:c>
-      <x:c r="B26" s="29" t="n">
-        <x:f>B25+12*D20</x:f>
+      <x:c r="B26" s="28" t="n">
         <x:v>56599</x:v>
       </x:c>
       <x:c r="C26" s="25" t="str">
-        <x:v>₽</x:v>
-      </x:c>
-      <x:c r="D26" s="25" t="str">
-        <x:v>Старт с техникой + 12 × ежемесячные</x:v>
-      </x:c>
-      <x:c r="E26" s="25" t="str">
         <x:v>Без музыкальных прав</x:v>
       </x:c>
+      <x:c r="D26" s="24"/>
+      <x:c r="E26" s="24"/>
       <x:c r="F26" s="24"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="30" t="str">
+      <x:c r="A27" s="27" t="str">
         <x:v>Первый год без новой техники</x:v>
       </x:c>
-      <x:c r="B27" s="29" t="n">
-        <x:f>B24+12*D20</x:f>
+      <x:c r="B27" s="28" t="n">
         <x:v>24599</x:v>
       </x:c>
       <x:c r="C27" s="25" t="str">
-        <x:v>₽</x:v>
-      </x:c>
-      <x:c r="D27" s="25" t="str">
-        <x:v>Старт без техники + 12 × ежемесячные</x:v>
-      </x:c>
-      <x:c r="E27" s="25" t="str">
         <x:v>Без музыкальных прав</x:v>
       </x:c>
+      <x:c r="D27" s="24"/>
+      <x:c r="E27" s="24"/>
       <x:c r="F27" s="24"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="30"/>
-      <x:c r="B28" s="30"/>
-      <x:c r="C28" s="25"/>
-      <x:c r="D28" s="25"/>
-      <x:c r="E28" s="25"/>
+      <x:c r="A28" s="24"/>
+      <x:c r="B28" s="24"/>
+      <x:c r="C28" s="24"/>
+      <x:c r="D28" s="24"/>
+      <x:c r="E28" s="24"/>
       <x:c r="F28" s="24"/>
     </x:row>
     <x:row r="29">
@@ -852,14 +760,14 @@
       <x:c r="F30" s="24"/>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
-      <x:c r="A31" s="31" t="str">
+      <x:c r="A31" s="30" t="str">
         <x:v>Допущения: домен, SSL, сайт и текущая серверная площадка уже есть. AzuraCast бесплатен. VPS и музыкальные права указаны ориентировочно. Цены RadioBOSS взяты с официального сайта; перед покупкой проверьте актуальную цену и статус оплаты.</x:v>
       </x:c>
-      <x:c r="B31" s="31"/>
-      <x:c r="C31" s="31"/>
-      <x:c r="D31" s="31"/>
-      <x:c r="E31" s="31"/>
-      <x:c r="F31" s="31"/>
+      <x:c r="B31" s="30"/>
+      <x:c r="C31" s="30"/>
+      <x:c r="D31" s="30"/>
+      <x:c r="E31" s="30"/>
+      <x:c r="F31" s="30"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
